--- a/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
+++ b/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,8 +40,70 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +114,36 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -93,6 +185,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -460,7 +585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -537,7 +662,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>D号屋</t>
+          <t>A号屋</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -556,7 +681,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>5551</v>
+        <v>8694</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -587,7 +712,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>F号屋</t>
+          <t>B号屋</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -606,7 +731,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5262</v>
+        <v>5616</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -637,48 +762,298 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>C号屋</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>5625</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>D号屋</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>5551</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>E号屋</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>7400</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>F号屋</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>5262</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>G号屋</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>5096</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>待售</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
           <t>H号屋</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>4+房</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>4963</v>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>待售</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -697,80 +1072,224 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>总价</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="1" ht="40" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>浅水湾108 - 独立屋销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="25" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>8 套</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>8 套</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>类型/位置</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>A号屋</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>B号屋</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>C号屋</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>D号屋</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>E号屋</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>F号屋</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>暂无</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>G号屋</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>H号屋</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>待售</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>暂无</t>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>独立屋</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>A号屋
+8694呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="C6" s="15" t="inlineStr">
+        <is>
+          <t>B号屋
+5616呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="inlineStr">
+        <is>
+          <t>C号屋
+5625呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>D号屋
+5551呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>E号屋
+7400呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>F号屋
+5262呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>G号屋
+5096呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>H号屋
+4963呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
+++ b/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
@@ -176,46 +176,46 @@
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>

--- a/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
+++ b/files/港岛-寿臣山及浅水湾-浅水湾108.xlsx
@@ -176,46 +176,46 @@
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
